--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,220 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129170290</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97530</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vålstocken SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>562246</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6624023</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Ungtallskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129170448</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97530</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vålstocken SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562237</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6623962</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Ingtallskog, inslag av gran, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97530</v>
+        <v>97533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97530</v>
+        <v>97533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97543</v>
+        <v>97550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97543</v>
+        <v>97550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97550</v>
+        <v>97552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97550</v>
+        <v>97552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97552</v>
+        <v>97578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97552</v>
+        <v>97578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97579</v>
+        <v>97580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97579</v>
+        <v>97580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97580</v>
+        <v>97584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97580</v>
+        <v>97584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97584</v>
+        <v>97586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97584</v>
+        <v>97586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97586</v>
+        <v>97590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97586</v>
+        <v>97590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97590</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>97601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>97601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62097-2024 artfynd.xlsx
+++ b/artfynd/A 62097-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>129170290</v>
       </c>
       <c r="B4" t="n">
-        <v>97601</v>
+        <v>97630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>129170448</v>
       </c>
       <c r="B5" t="n">
-        <v>97601</v>
+        <v>97630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
